--- a/models/6365_SOTP_Model.xlsx
+++ b/models/6365_SOTP_Model.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>DCF — Perpetuity Growth</t>
+          <t>DCF - Perpetuity Growth</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
@@ -729,7 +729,7 @@
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>DCF — Exit Multiple</t>
+          <t>DCF - Exit Multiple</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
@@ -743,7 +743,7 @@
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Comps — EV/EBITDA</t>
+          <t>Comps - EV/EBITDA Median</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
@@ -757,7 +757,7 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Comps — PER</t>
+          <t>Comps - PER Median</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -766,6 +766,13 @@
       <c r="D16" s="10">
         <f>(C16-$C$12)/$C$12</f>
         <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>DCF cross-check as of 2026-09-06 23:29 from 6365_DCF_Model_20260413.xlsx (static snapshot — regenerate after re-running the DCF)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1929,6 +1936,11 @@
         <f>C24*1000/C25/C26</f>
         <v/>
       </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Fair Value = Equity Value (¥M) × 1,000 ÷ Shares (千株) ÷ split. 株数は【千株】単位（dcf_comps_template は【株】単位: 桁が3つ違う）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2266,7 +2278,7 @@
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Fair Value (¥/share, post-split) — Base discount, base Aero multiple</t>
+          <t>Fair Value (¥/share, post-split) — Base discount, base Overseas &amp; Desalination (DeROs + Export) multiple</t>
         </is>
       </c>
     </row>
@@ -2297,23 +2309,23 @@
         <v>5</v>
       </c>
       <c r="C26" s="59">
-        <f>(($E$6*$B26+$E$7*C$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B26+$E$7*C$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="D26" s="59">
-        <f>(($E$6*$B26+$E$7*D$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B26+$E$7*D$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="E26" s="59">
-        <f>(($E$6*$B26+$E$7*E$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B26+$E$7*E$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="F26" s="59">
-        <f>(($E$6*$B26+$E$7*F$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B26+$E$7*F$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="G26" s="59">
-        <f>(($E$6*$B26+$E$7*G$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B26+$E$7*G$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
     </row>
@@ -2322,23 +2334,23 @@
         <v>6</v>
       </c>
       <c r="C27" s="59">
-        <f>(($E$6*$B27+$E$7*C$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B27+$E$7*C$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="D27" s="59">
-        <f>(($E$6*$B27+$E$7*D$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B27+$E$7*D$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="E27" s="59">
-        <f>(($E$6*$B27+$E$7*E$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B27+$E$7*E$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="F27" s="59">
-        <f>(($E$6*$B27+$E$7*F$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B27+$E$7*F$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="G27" s="59">
-        <f>(($E$6*$B27+$E$7*G$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B27+$E$7*G$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
     </row>
@@ -2347,23 +2359,23 @@
         <v>7</v>
       </c>
       <c r="C28" s="59">
-        <f>(($E$6*$B28+$E$7*C$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B28+$E$7*C$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="D28" s="59">
-        <f>(($E$6*$B28+$E$7*D$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B28+$E$7*D$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="E28" s="59">
-        <f>(($E$6*$B28+$E$7*E$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B28+$E$7*E$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="F28" s="59">
-        <f>(($E$6*$B28+$E$7*F$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B28+$E$7*F$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="G28" s="59">
-        <f>(($E$6*$B28+$E$7*G$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B28+$E$7*G$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
     </row>
@@ -2372,23 +2384,23 @@
         <v>8</v>
       </c>
       <c r="C29" s="59">
-        <f>(($E$6*$B29+$E$7*C$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B29+$E$7*C$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="D29" s="59">
-        <f>(($E$6*$B29+$E$7*D$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B29+$E$7*D$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="E29" s="59">
-        <f>(($E$6*$B29+$E$7*E$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B29+$E$7*E$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="F29" s="59">
-        <f>(($E$6*$B29+$E$7*F$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B29+$E$7*F$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="G29" s="59">
-        <f>(($E$6*$B29+$E$7*G$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B29+$E$7*G$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
     </row>
@@ -2397,23 +2409,23 @@
         <v>9</v>
       </c>
       <c r="C30" s="59">
-        <f>(($E$6*$B30+$E$7*C$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B30+$E$7*C$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="D30" s="59">
-        <f>(($E$6*$B30+$E$7*D$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B30+$E$7*D$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="E30" s="59">
-        <f>(($E$6*$B30+$E$7*E$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B30+$E$7*E$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="F30" s="59">
-        <f>(($E$6*$B30+$E$7*F$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B30+$E$7*F$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
       <c r="G30" s="59">
-        <f>(($E$6*$B30+$E$7*G$25+$E$8*$F$8+$C$9)*(1-0.0)-$C$10-$C$11)*1000/$C$12/$C$13</f>
+        <f>(($E$6*$B30+$E$7*G$25+$E$8*$F$8+$C$9)*(1-'SOTP Valuation'!$C$20)-$C$10-$C$11)*1000/$C$12/$C$13</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E19"/>
+  <dimension ref="B1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2449,14 +2461,14 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>IHI does not disclose segment-level D&amp;A.</t>
+          <t>セグメント別D&amp;Aは非開示のため、固定資産集約度をもとに按分している。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Allocation is estimated based on fixed asset intensity by segment.</t>
+          <t>Segment-level D&amp;A is not disclosed; allocation is estimated from fixed-asset intensity by segment.</t>
         </is>
       </c>
     </row>
@@ -2568,45 +2580,13 @@
     <row r="15">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>• Aero segment has highest capital intensity (engine test facilities, MRO hangars)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>• Energy segment includes boiler/turbine manufacturing → moderate fixed assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>• Industrial includes turbocharger plants (Niigata, overseas) → moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>• Social Infrastructure: project-based, lower owned fixed assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr">
-        <is>
           <t>• Allocation sums to 100% — residual is implicitly in corporate/eliminations</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B16:E16"/>
+  <mergeCells count="1">
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
